--- a/Normalisation Task.xlsx
+++ b/Normalisation Task.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ngc1-my.sharepoint.com/personal/fiaz_ali_ngc_co_tt/Documents/Desktop/FIAZ/Essex/Deciphering Big Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="350" documentId="8_{4B51BD7F-555F-4379-9E9A-BDE4CAA376C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EF46494-75F8-4249-A024-044DEFDFA0D9}"/>
+  <xr:revisionPtr revIDLastSave="351" documentId="8_{4B51BD7F-555F-4379-9E9A-BDE4CAA376C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CB957E2-6F02-440F-9E65-7F8361FC26A5}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{19FDF363-F5B7-4F53-B56A-113C3C8DD361}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="65">
   <si>
     <t>Student Number  </t>
   </si>
@@ -317,6 +317,9 @@
       </rPr>
       <t>(Same as 2NF - Each table attribute depends on PK and no non-key attribute depend on another non-key attribute.)</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Teacher Name </t>
   </si>
 </sst>
 </file>
@@ -442,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -468,97 +471,70 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -879,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F19B2C-F344-42A0-90F5-191EC717E402}">
-  <dimension ref="A1:R116"/>
+  <dimension ref="A1:Q114"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.453125" style="1" customWidth="1"/>
@@ -894,45 +870,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="31">
+      <c r="A2" s="26">
         <v>1001</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="31">
+      <c r="C2" s="26">
         <v>78</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="27">
         <v>37128</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -946,11 +922,11 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="27"/>
       <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
@@ -962,11 +938,11 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="4" t="s">
         <v>11</v>
       </c>
@@ -978,19 +954,19 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="31">
+      <c r="A5" s="26">
         <v>1002</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="26">
         <v>55</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="27">
         <v>36435</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1004,11 +980,11 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="31"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="32"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="27"/>
       <c r="F6" s="4" t="s">
         <v>20</v>
       </c>
@@ -1020,11 +996,11 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="31"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="32"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="4" t="s">
         <v>21</v>
       </c>
@@ -1036,19 +1012,19 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="31">
+      <c r="A8" s="26">
         <v>1003</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="26">
         <v>90</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="27">
         <v>34855</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -1062,11 +1038,11 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="32"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="27"/>
       <c r="F9" s="4" t="s">
         <v>10</v>
       </c>
@@ -1078,11 +1054,11 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="32"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="27"/>
       <c r="F10" s="4" t="s">
         <v>11</v>
       </c>
@@ -1094,19 +1070,19 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="31">
+      <c r="A11" s="26">
         <v>1004</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="26">
         <v>70</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="27">
         <v>29436</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -1120,11 +1096,11 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="31"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="32"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="27"/>
       <c r="F12" s="4" t="s">
         <v>11</v>
       </c>
@@ -1136,11 +1112,11 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="31"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="27"/>
       <c r="F13" s="4" t="s">
         <v>20</v>
       </c>
@@ -1152,19 +1128,19 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="31">
+      <c r="A14" s="26">
         <v>1005</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="26">
         <v>45</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="27">
         <v>37377</v>
       </c>
       <c r="F14" s="4" t="s">
@@ -1178,11 +1154,11 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="31"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="32"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="4" t="s">
         <v>10</v>
       </c>
@@ -1194,11 +1170,11 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="31"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="32"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="27"/>
       <c r="F16" s="4" t="s">
         <v>21</v>
       </c>
@@ -1209,48 +1185,44 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19" s="33" t="s">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A19" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="E19" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="33" t="s">
+      <c r="H19" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I19" s="21"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J19" s="11"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="9"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="9"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>1001</v>
       </c>
@@ -1275,18 +1247,15 @@
       <c r="H20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="21"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="27"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J20" s="11"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="9"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>1001</v>
       </c>
@@ -1311,18 +1280,15 @@
       <c r="H21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="21"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="27"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J21" s="2"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="9"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>1001</v>
       </c>
@@ -1347,18 +1313,15 @@
       <c r="H22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="21"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="27"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J22" s="2"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="9"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>1002</v>
       </c>
@@ -1383,18 +1346,15 @@
       <c r="H23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I23" s="21"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="27"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J23" s="2"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="9"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>1002</v>
       </c>
@@ -1419,18 +1379,15 @@
       <c r="H24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="21"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="27"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J24" s="2"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="9"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>1002</v>
       </c>
@@ -1455,18 +1412,15 @@
       <c r="H25" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I25" s="21"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="27"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J25" s="2"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="9"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>1003</v>
       </c>
@@ -1491,18 +1445,14 @@
       <c r="H26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I26" s="21"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J26" s="2"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="9"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="9"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>1003</v>
       </c>
@@ -1527,18 +1477,11 @@
       <c r="H27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="21"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J27" s="2"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>1003</v>
       </c>
@@ -1563,18 +1506,11 @@
       <c r="H28" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="21"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J28" s="2"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>1004</v>
       </c>
@@ -1599,18 +1535,11 @@
       <c r="H29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I29" s="21"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="21"/>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J29" s="2"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="9"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>1004</v>
       </c>
@@ -1635,18 +1564,11 @@
       <c r="H30" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="21"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J30" s="2"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="9"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>1004</v>
       </c>
@@ -1671,18 +1593,11 @@
       <c r="H31" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="21"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="21"/>
-      <c r="P31" s="21"/>
-      <c r="Q31" s="21"/>
-      <c r="R31" s="21"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J31" s="2"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="9"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>1005</v>
       </c>
@@ -1707,18 +1622,11 @@
       <c r="H32" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="21"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
-      <c r="O32" s="21"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="21"/>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J32" s="2"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="9"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>1005</v>
       </c>
@@ -1743,18 +1651,11 @@
       <c r="H33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I33" s="21"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J33" s="2"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="9"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>1005</v>
       </c>
@@ -1779,95 +1680,64 @@
       <c r="H34" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I34" s="21"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21"/>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="21"/>
-      <c r="R34" s="21"/>
-    </row>
-    <row r="35" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J34" s="2"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="9"/>
+    </row>
+    <row r="35" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="3"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="21"/>
-      <c r="N35" s="21"/>
-      <c r="O35" s="21"/>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="21"/>
-      <c r="R35" s="21"/>
-    </row>
-    <row r="36" spans="1:18" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="29" t="s">
+      <c r="J35" s="2"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="29"/>
+      <c r="B36" s="30"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="3"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="21"/>
-      <c r="N36" s="21"/>
-      <c r="O36" s="21"/>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="21"/>
-      <c r="R36" s="21"/>
-    </row>
-    <row r="37" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="7" t="s">
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="39"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="21"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="21"/>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="21"/>
-      <c r="R37" s="21"/>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A38" s="34" t="s">
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="33" t="s">
+      <c r="C38" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="33" t="s">
+      <c r="D38" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E38" s="33" t="s">
+      <c r="E38" s="20" t="s">
         <v>4</v>
       </c>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>1001</v>
       </c>
@@ -1885,7 +1755,7 @@
       </c>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>1002</v>
       </c>
@@ -1902,7 +1772,7 @@
         <v>36435</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>1003</v>
       </c>
@@ -1919,7 +1789,7 @@
         <v>34855</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>1004</v>
       </c>
@@ -1936,7 +1806,7 @@
         <v>29436</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>1005</v>
       </c>
@@ -1953,41 +1823,41 @@
         <v>37377</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A45" s="7" t="s">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A45" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-    </row>
-    <row r="46" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="34" t="s">
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+    </row>
+    <row r="46" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="34" t="s">
+      <c r="B46" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="10"/>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="C46" s="7"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="11"/>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="C47" s="9"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="11"/>
+      <c r="C48" s="9"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
@@ -1996,7 +1866,7 @@
       <c r="B49" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="11"/>
+      <c r="C49" s="9"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
@@ -2005,7 +1875,7 @@
       <c r="B50" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="9"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
@@ -2014,30 +1884,30 @@
       <c r="B51" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C51" s="11"/>
+      <c r="C51" s="9"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="34" t="s">
+      <c r="A54" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B54" s="34" t="s">
+      <c r="B54" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C54" s="10"/>
+      <c r="C54" s="7"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
@@ -2046,7 +1916,7 @@
       <c r="B55" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="11"/>
+      <c r="C55" s="9"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
@@ -2055,7 +1925,7 @@
       <c r="B56" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C56" s="11"/>
+      <c r="C56" s="9"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
@@ -2064,7 +1934,7 @@
       <c r="B57" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C57" s="11"/>
+      <c r="C57" s="9"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
@@ -2073,7 +1943,7 @@
       <c r="B58" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C58" s="11"/>
+      <c r="C58" s="9"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="s">
@@ -2082,30 +1952,30 @@
       <c r="B59" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C59" s="11"/>
+      <c r="C59" s="9"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="11"/>
+      <c r="A60" s="9"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="9"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="34" t="s">
+      <c r="A62" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B62" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C62" s="10"/>
+      <c r="B62" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C62" s="7"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
@@ -2115,7 +1985,7 @@
         <f t="shared" ref="B63:B67" si="0">H20</f>
         <v>Mr Jones</v>
       </c>
-      <c r="C63" s="11"/>
+      <c r="C63" s="9"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
@@ -2125,9 +1995,9 @@
         <f t="shared" si="0"/>
         <v>Ms Parker</v>
       </c>
-      <c r="C64" s="11"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C64" s="9"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
         <v>44</v>
       </c>
@@ -2135,18 +2005,18 @@
         <f t="shared" si="0"/>
         <v>Mr Peters</v>
       </c>
-      <c r="C65" s="11"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C65" s="9"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C66" s="11"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C66" s="9"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="8" t="s">
         <v>47</v>
       </c>
@@ -2154,42 +2024,41 @@
         <f t="shared" si="0"/>
         <v>Mrs Patel</v>
       </c>
-      <c r="C67" s="11"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" s="11"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="11"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" s="13"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="11"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70" s="15" t="s">
+      <c r="C67" s="9"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="9"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="9"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="10"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="9"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B70" s="12"/>
-      <c r="C70" s="11"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="35" t="s">
+      <c r="B70" s="2"/>
+      <c r="C70" s="9"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B71" s="33" t="s">
+      <c r="B71" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C71" s="34" t="s">
+      <c r="C71" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D71" s="36" t="s">
+      <c r="D71" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E71" s="17"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="19" t="s">
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="13" t="s">
         <v>50</v>
       </c>
       <c r="B72" s="8" t="s">
@@ -2201,10 +2070,9 @@
       <c r="D72" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E72" s="17"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A73" s="19" t="s">
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="13" t="s">
         <v>51</v>
       </c>
       <c r="B73" s="8" t="s">
@@ -2216,10 +2084,9 @@
       <c r="D73" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E73" s="17"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74" s="19" t="s">
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -2231,10 +2098,9 @@
       <c r="D74" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E74" s="17"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A75" s="19" t="s">
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="13" t="s">
         <v>53</v>
       </c>
       <c r="B75" s="8" t="s">
@@ -2246,10 +2112,9 @@
       <c r="D75" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E75" s="17"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A76" s="19" t="s">
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B76" s="8" t="s">
@@ -2261,388 +2126,288 @@
       <c r="D76" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E76" s="17"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A77" s="19" t="s">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D77" s="20" t="s">
+      <c r="D77" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E77" s="17"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A78" s="14"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="17"/>
-      <c r="E78" s="17"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A79" s="14" t="s">
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="11"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="9"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B79" s="16"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A80" s="37" t="s">
+      <c r="B79" s="2"/>
+      <c r="C79" s="9"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B80" s="38" t="s">
+      <c r="B80" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C80" s="11"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C80" s="9"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>1001</v>
       </c>
-      <c r="B81" s="19" t="s">
+      <c r="B81" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C81" s="11"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C81" s="9"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="4">
         <v>1001</v>
       </c>
-      <c r="B82" s="19" t="s">
+      <c r="B82" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C82" s="11"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C82" s="9"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>1001</v>
       </c>
-      <c r="B83" s="19" t="s">
+      <c r="B83" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C83" s="11"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C83" s="9"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="4">
         <v>1002</v>
       </c>
-      <c r="B84" s="19" t="s">
+      <c r="B84" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C84" s="11"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C84" s="9"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
         <v>1002</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="B85" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C85" s="11"/>
-      <c r="D85" s="17"/>
-      <c r="E85" s="17"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C85" s="9"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="4">
         <v>1002</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="B86" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C86" s="11"/>
-      <c r="D86" s="17"/>
-      <c r="E86" s="17"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C86" s="9"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="4">
         <v>1003</v>
       </c>
-      <c r="B87" s="19" t="s">
+      <c r="B87" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C87" s="11"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="17"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C87" s="9"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="4">
         <v>1003</v>
       </c>
-      <c r="B88" s="19" t="s">
+      <c r="B88" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C88" s="11"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="17"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C88" s="9"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="4">
         <v>1003</v>
       </c>
-      <c r="B89" s="19" t="s">
+      <c r="B89" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C89" s="11"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="17"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C89" s="9"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="4">
         <v>1004</v>
       </c>
-      <c r="B90" s="19" t="s">
+      <c r="B90" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C90" s="11"/>
-      <c r="D90" s="17"/>
-      <c r="E90" s="17"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C90" s="9"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="4">
         <v>1004</v>
       </c>
-      <c r="B91" s="19" t="s">
+      <c r="B91" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C91" s="11"/>
-      <c r="D91" s="17"/>
-      <c r="E91" s="17"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C91" s="9"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="4">
         <v>1004</v>
       </c>
-      <c r="B92" s="19" t="s">
+      <c r="B92" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C92" s="11"/>
-      <c r="D92" s="17"/>
-      <c r="E92" s="17"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C92" s="9"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
         <v>1005</v>
       </c>
-      <c r="B93" s="19" t="s">
+      <c r="B93" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C93" s="11"/>
-      <c r="D93" s="17"/>
-      <c r="E93" s="17"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C93" s="9"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="4">
         <v>1005</v>
       </c>
-      <c r="B94" s="19" t="s">
+      <c r="B94" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C94" s="11"/>
-      <c r="D94" s="17"/>
-      <c r="E94" s="17"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C94" s="9"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="4">
         <v>1005</v>
       </c>
-      <c r="B95" s="19" t="s">
+      <c r="B95" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C95" s="18"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="17"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" s="12"/>
-      <c r="B96" s="16"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="17"/>
-      <c r="E96" s="17"/>
+      <c r="C95" s="2"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
     </row>
     <row r="97" spans="1:7" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="29" t="s">
+      <c r="A97" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="B97" s="29"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="29"/>
-      <c r="E97" s="29"/>
-      <c r="F97" s="29"/>
-      <c r="G97" s="29"/>
+      <c r="B97" s="30"/>
+      <c r="C97" s="30"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="30"/>
     </row>
     <row r="98" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="30"/>
-      <c r="B98" s="30"/>
-      <c r="C98" s="30"/>
-      <c r="D98" s="30"/>
-      <c r="E98" s="30"/>
+      <c r="A98" s="19"/>
+      <c r="B98" s="19"/>
+      <c r="C98" s="19"/>
+      <c r="D98" s="19"/>
+      <c r="E98" s="19"/>
     </row>
     <row r="99" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="30"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="30"/>
-      <c r="D99" s="30"/>
-      <c r="E99" s="30"/>
+      <c r="A99" s="19"/>
+      <c r="B99" s="19"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="19"/>
+      <c r="E99" s="19"/>
     </row>
     <row r="100" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="12"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="12"/>
-      <c r="D100" s="21"/>
-      <c r="E100" s="21"/>
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101" s="12"/>
-      <c r="B101" s="12"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21"/>
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A102" s="12"/>
-      <c r="B102" s="12"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="21"/>
-      <c r="E102" s="21"/>
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A103" s="12"/>
-      <c r="B103" s="12"/>
-      <c r="C103" s="12"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A104" s="12"/>
-      <c r="B104" s="12"/>
-      <c r="C104" s="12"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="21"/>
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105" s="12"/>
-      <c r="B105" s="12"/>
-      <c r="C105" s="12"/>
-      <c r="D105" s="21"/>
-      <c r="E105" s="21"/>
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
     </row>
     <row r="106" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="12"/>
-      <c r="B106" s="12"/>
-      <c r="C106" s="12"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="21"/>
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A107" s="12"/>
-      <c r="B107" s="12"/>
-      <c r="C107" s="12"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="21"/>
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" s="12"/>
-      <c r="B108" s="12"/>
-      <c r="C108" s="12"/>
-      <c r="D108" s="21"/>
-      <c r="E108" s="21"/>
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A109" s="12"/>
-      <c r="B109" s="12"/>
-      <c r="C109" s="12"/>
-      <c r="D109" s="21"/>
-      <c r="E109" s="21"/>
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A110" s="12"/>
-      <c r="B110" s="12"/>
-      <c r="C110" s="12"/>
-      <c r="D110" s="21"/>
-      <c r="E110" s="21"/>
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A111" s="12"/>
-      <c r="B111" s="12"/>
-      <c r="C111" s="12"/>
-      <c r="D111" s="21"/>
-      <c r="E111" s="21"/>
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
     </row>
     <row r="112" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="12"/>
-      <c r="B112" s="12"/>
-      <c r="C112" s="12"/>
-      <c r="D112" s="21"/>
-      <c r="E112" s="21"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A113" s="12"/>
-      <c r="B113" s="12"/>
-      <c r="C113" s="12"/>
-      <c r="D113" s="21"/>
-      <c r="E113" s="21"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A114" s="12"/>
-      <c r="B114" s="12"/>
-      <c r="C114" s="12"/>
-      <c r="D114" s="21"/>
-      <c r="E114" s="21"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A115" s="21"/>
-      <c r="B115" s="21"/>
-      <c r="C115" s="21"/>
-      <c r="D115" s="21"/>
-      <c r="E115" s="21"/>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A116" s="21"/>
-      <c r="B116" s="21"/>
-      <c r="C116" s="21"/>
-      <c r="D116" s="21"/>
-      <c r="E116" s="21"/>
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="B14:B16"/>
@@ -2650,10 +2415,26 @@
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="E14:E16"/>
     <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A97:G97"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
